--- a/workspace/framework_paper/edf/edf-15/edf-15_times.xlsx
+++ b/workspace/framework_paper/edf/edf-15/edf-15_times.xlsx
@@ -438,13 +438,13 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.004475654908455909</v>
+        <v>0.0034768399852328</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009180180933326483</v>
+        <v>0.00828864841721952</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09187103460077196</v>
+        <v>0.005314134154468774</v>
       </c>
     </row>
     <row r="3">
@@ -452,13 +452,13 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.005556176693644375</v>
+        <v>0.003711785834748298</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009035609131678939</v>
+        <v>0.008099118401296436</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1282619577180594</v>
+        <v>0.006118130744434893</v>
       </c>
     </row>
     <row r="4">
@@ -466,13 +466,13 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.005725494166836142</v>
+        <v>0.00462902499595657</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0102996817138046</v>
+        <v>0.009029241669923067</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2081459870934486</v>
+        <v>0.005910758380778134</v>
       </c>
     </row>
     <row r="5">
@@ -480,13 +480,13 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.006258653218392283</v>
+        <v>0.005055269966833293</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01136325403116643</v>
+        <v>0.0102256665751338</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7434909703582525</v>
+        <v>0.007199408253654838</v>
       </c>
     </row>
     <row r="6">
@@ -494,13 +494,13 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01390382061712444</v>
+        <v>0.01294651078991592</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05014950239099562</v>
+        <v>0.04800986477173865</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4351918746251613</v>
+        <v>0.2058267559064552</v>
       </c>
     </row>
     <row r="7">
@@ -508,13 +508,13 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.006602336633950472</v>
+        <v>0.006031404987443239</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06379228820092976</v>
+        <v>0.05595281668007374</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6410179621167481</v>
+        <v>0.04139015621505678</v>
       </c>
     </row>
     <row r="8">
@@ -522,13 +522,13 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.007021466651931405</v>
+        <v>0.007000460792332888</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1318877951521426</v>
+        <v>0.117875981638208</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7143888735771179</v>
+        <v>0.05211552135646343</v>
       </c>
     </row>
     <row r="9">
@@ -536,13 +536,13 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.007643931587226689</v>
+        <v>0.008034937568008899</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1275507478136569</v>
+        <v>0.1126392915099859</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9128986129257828</v>
+        <v>0.1055964924953878</v>
       </c>
     </row>
     <row r="10">
@@ -550,13 +550,13 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.008988009993918239</v>
+        <v>0.009042278346605599</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1506805395893752</v>
+        <v>0.130054562240839</v>
       </c>
       <c r="D10" t="n">
-        <v>1.534199603740126</v>
+        <v>0.1086060121562332</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +564,13 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.009918977452907712</v>
+        <v>0.009372260048985481</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1884182826150209</v>
+        <v>0.1655705224722624</v>
       </c>
       <c r="D11" t="n">
-        <v>1.848337378762662</v>
+        <v>0.2043951051775366</v>
       </c>
     </row>
     <row r="12">
@@ -578,13 +578,13 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01001310576684773</v>
+        <v>0.009035834968090057</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2235030895378441</v>
+        <v>0.2014774566609412</v>
       </c>
       <c r="D12" t="n">
-        <v>3.784920157603919</v>
+        <v>0.3368364319577813</v>
       </c>
     </row>
     <row r="13">
@@ -592,13 +592,13 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01125420832308009</v>
+        <v>0.0114194725244306</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4329226049594581</v>
+        <v>0.4150282405409962</v>
       </c>
       <c r="D13" t="n">
-        <v>4.655550686120987</v>
+        <v>1.00447624287568</v>
       </c>
     </row>
     <row r="14">
@@ -606,13 +606,13 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.03047217816580087</v>
+        <v>0.02929706229595468</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5240187557693571</v>
+        <v>0.5207959087658673</v>
       </c>
       <c r="D14" t="n">
-        <v>7.258523945808411</v>
+        <v>2.247880308786407</v>
       </c>
     </row>
     <row r="15">
@@ -620,13 +620,13 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.03645481343148276</v>
+        <v>0.03657004995737225</v>
       </c>
       <c r="C15" t="n">
-        <v>1.327711949944496</v>
+        <v>1.330719084776938</v>
       </c>
       <c r="D15" t="n">
-        <v>13.65223710179329</v>
+        <v>6.913393665188924</v>
       </c>
     </row>
     <row r="16">
@@ -634,13 +634,13 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01439919577911496</v>
+        <v>0.01443113336106762</v>
       </c>
       <c r="C16" t="n">
-        <v>1.727025984413922</v>
+        <v>1.700758986584842</v>
       </c>
       <c r="D16" t="n">
-        <v>22.27755202293396</v>
+        <v>8.956068995967508</v>
       </c>
     </row>
     <row r="17">
@@ -648,13 +648,13 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01476486820494756</v>
+        <v>0.01468216902809218</v>
       </c>
       <c r="C17" t="n">
-        <v>5.912284026648849</v>
+        <v>5.818757697790861</v>
       </c>
       <c r="D17" t="n">
-        <v>34.23514800786972</v>
+        <v>17.44493404673413</v>
       </c>
     </row>
     <row r="18">
@@ -662,13 +662,13 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01292115574236959</v>
+        <v>0.01335452664876357</v>
       </c>
       <c r="C18" t="n">
-        <v>5.840389088727534</v>
+        <v>5.789505921900273</v>
       </c>
       <c r="D18" t="n">
-        <v>72.23045031309128</v>
+        <v>45.67307746153325</v>
       </c>
     </row>
     <row r="19">
@@ -676,13 +676,13 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01757752015255392</v>
+        <v>0.01809049419593066</v>
       </c>
       <c r="C19" t="n">
-        <v>16.57268610842526</v>
+        <v>15.57766553293914</v>
       </c>
       <c r="D19" t="n">
-        <v>145.2287257671356</v>
+        <v>79.22795805597679</v>
       </c>
     </row>
     <row r="20">
@@ -690,13 +690,13 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01965791231021285</v>
+        <v>0.019553625844419</v>
       </c>
       <c r="C20" t="n">
-        <v>21.00676769144833</v>
+        <v>21.17243868276477</v>
       </c>
       <c r="D20" t="n">
-        <v>211.3442776012421</v>
+        <v>116.4271141236648</v>
       </c>
     </row>
     <row r="21">
@@ -704,13 +704,13 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.01498268345138058</v>
+        <v>0.01500333506381139</v>
       </c>
       <c r="C21" t="n">
-        <v>27.83918901138007</v>
+        <v>27.83569107577205</v>
       </c>
       <c r="D21" t="n">
-        <v>375.221693315506</v>
+        <v>265.5558716144413</v>
       </c>
     </row>
   </sheetData>
